--- a/dados.xlsx
+++ b/dados.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://iterpar-my.sharepoint.com/personal/emilly_viana_iter_com_br/Documents/Documentos/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Emilly.viana\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="29" documentId="8_{20F928C2-79CC-43B2-BEC9-E52AE67EF152}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3B9F0A5F-683B-4D87-B8EA-065DCD842E54}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5221E2D3-ABFE-4682-B195-1291A0CFE842}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" firstSheet="2" activeTab="2" xr2:uid="{0C296C70-2B95-4077-8DDD-908C1E65EBA2}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" firstSheet="1" activeTab="2" xr2:uid="{0C296C70-2B95-4077-8DDD-908C1E65EBA2}"/>
   </bookViews>
   <sheets>
     <sheet name="Índices anuais" sheetId="3" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="44">
   <si>
     <t>Mês</t>
   </si>
@@ -183,8 +183,8 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="3">
     <numFmt numFmtId="6" formatCode="&quot;R$&quot;\ #,##0;[Red]\-&quot;R$&quot;\ #,##0"/>
-    <numFmt numFmtId="172" formatCode="&quot;R$&quot;\ #,##0"/>
-    <numFmt numFmtId="173" formatCode="0.0"/>
+    <numFmt numFmtId="164" formatCode="&quot;R$&quot;\ #,##0"/>
+    <numFmt numFmtId="165" formatCode="0.0"/>
   </numFmts>
   <fonts count="4" x14ac:knownFonts="1">
     <font>
@@ -242,7 +242,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -262,17 +262,11 @@
     <xf numFmtId="6" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="172" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="6" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
@@ -284,19 +278,19 @@
     <xf numFmtId="9" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="173" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="173" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -306,13 +300,6 @@
   </cellStyles>
   <dxfs count="42">
     <dxf>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="10" formatCode="&quot;R$&quot;\ #,##0;[Red]\-&quot;R$&quot;\ #,##0"/>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -334,43 +321,75 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="10" formatCode="&quot;R$&quot;\ #,##0;[Red]\-&quot;R$&quot;\ #,##0"/>
+      <numFmt numFmtId="13" formatCode="0%"/>
       <fill>
         <patternFill patternType="solid">
           <fgColor indexed="64"/>
           <bgColor rgb="FFF7F5FA"/>
         </patternFill>
       </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="10" formatCode="&quot;R$&quot;\ #,##0;[Red]\-&quot;R$&quot;\ #,##0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
       <fill>
         <patternFill patternType="solid">
           <fgColor indexed="64"/>
           <bgColor rgb="FFF7F5FA"/>
         </patternFill>
       </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="10" formatCode="&quot;R$&quot;\ #,##0;[Red]\-&quot;R$&quot;\ #,##0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
       <fill>
         <patternFill patternType="solid">
           <fgColor indexed="64"/>
           <bgColor rgb="FFF7F5FA"/>
         </patternFill>
       </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="10" formatCode="&quot;R$&quot;\ #,##0;[Red]\-&quot;R$&quot;\ #,##0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
       <fill>
         <patternFill patternType="solid">
           <fgColor indexed="64"/>
           <bgColor rgb="FFF7F5FA"/>
         </patternFill>
       </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFF7F5FA"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="10" formatCode="&quot;R$&quot;\ #,##0;[Red]\-&quot;R$&quot;\ #,##0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="10" formatCode="&quot;R$&quot;\ #,##0;[Red]\-&quot;R$&quot;\ #,##0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="10" formatCode="&quot;R$&quot;\ #,##0;[Red]\-&quot;R$&quot;\ #,##0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="10" formatCode="&quot;R$&quot;\ #,##0;[Red]\-&quot;R$&quot;\ #,##0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="10" formatCode="&quot;R$&quot;\ #,##0;[Red]\-&quot;R$&quot;\ #,##0"/>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -405,12 +424,6 @@
         <scheme val="minor"/>
       </font>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -445,53 +458,71 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="10" formatCode="&quot;R$&quot;\ #,##0;[Red]\-&quot;R$&quot;\ #,##0"/>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="10" formatCode="&quot;R$&quot;\ #,##0;[Red]\-&quot;R$&quot;\ #,##0"/>
       <fill>
         <patternFill patternType="solid">
           <fgColor indexed="64"/>
           <bgColor rgb="FFF7F5FA"/>
         </patternFill>
       </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="13" formatCode="0%"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="10" formatCode="&quot;R$&quot;\ #,##0;[Red]\-&quot;R$&quot;\ #,##0"/>
       <fill>
         <patternFill patternType="solid">
           <fgColor indexed="64"/>
           <bgColor rgb="FFF7F5FA"/>
         </patternFill>
       </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="10" formatCode="&quot;R$&quot;\ #,##0;[Red]\-&quot;R$&quot;\ #,##0"/>
       <fill>
         <patternFill patternType="solid">
           <fgColor indexed="64"/>
           <bgColor rgb="FFF7F5FA"/>
         </patternFill>
       </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="10" formatCode="&quot;R$&quot;\ #,##0;[Red]\-&quot;R$&quot;\ #,##0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="10" formatCode="&quot;R$&quot;\ #,##0;[Red]\-&quot;R$&quot;\ #,##0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="10" formatCode="&quot;R$&quot;\ #,##0;[Red]\-&quot;R$&quot;\ #,##0"/>
       <fill>
         <patternFill patternType="solid">
           <fgColor indexed="64"/>
           <bgColor rgb="FFF7F5FA"/>
         </patternFill>
       </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFF7F5FA"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -512,43 +543,6 @@
       </font>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="10" formatCode="&quot;R$&quot;\ #,##0;[Red]\-&quot;R$&quot;\ #,##0"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="10" formatCode="&quot;R$&quot;\ #,##0;[Red]\-&quot;R$&quot;\ #,##0"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="10" formatCode="&quot;R$&quot;\ #,##0;[Red]\-&quot;R$&quot;\ #,##0"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="10" formatCode="&quot;R$&quot;\ #,##0;[Red]\-&quot;R$&quot;\ #,##0"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="10" formatCode="&quot;R$&quot;\ #,##0;[Red]\-&quot;R$&quot;\ #,##0"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="10" formatCode="&quot;R$&quot;\ #,##0;[Red]\-&quot;R$&quot;\ #,##0"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="10" formatCode="&quot;R$&quot;\ #,##0;[Red]\-&quot;R$&quot;\ #,##0"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -563,77 +557,77 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{F6ECEC96-5B32-417A-B576-72EA3EFF4E37}" name="Tabela2" displayName="Tabela2" ref="A2:E10" totalsRowShown="0" headerRowDxfId="19" dataDxfId="18">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{F6ECEC96-5B32-417A-B576-72EA3EFF4E37}" name="Tabela2" displayName="Tabela2" ref="A2:E10" totalsRowShown="0" headerRowDxfId="30" dataDxfId="29">
   <autoFilter ref="A2:E10" xr:uid="{F6ECEC96-5B32-417A-B576-72EA3EFF4E37}"/>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{C0180337-7CC7-48BB-B869-2C3B07C11F1E}" name="Ano" dataDxfId="24"/>
-    <tableColumn id="2" xr3:uid="{100FB33F-2FA4-4607-B730-06D9395F8731}" name="Média anual informada no relatório" dataDxfId="23"/>
-    <tableColumn id="3" xr3:uid="{DB6F75DE-665E-4418-A0DC-A12E54EFCE7B}" name="Antecedência (dias)" dataDxfId="22"/>
-    <tableColumn id="4" xr3:uid="{F927B6C4-566E-48E9-9552-8EFC3D5F2C94}" name="Estadia (dias)" dataDxfId="21"/>
-    <tableColumn id="5" xr3:uid="{D989CA06-7171-4BB8-B0F0-15BE78123C53}" name="Cancelamento" dataDxfId="20"/>
+    <tableColumn id="1" xr3:uid="{C0180337-7CC7-48BB-B869-2C3B07C11F1E}" name="Ano" dataDxfId="28"/>
+    <tableColumn id="2" xr3:uid="{100FB33F-2FA4-4607-B730-06D9395F8731}" name="Média anual informada no relatório" dataDxfId="27"/>
+    <tableColumn id="3" xr3:uid="{DB6F75DE-665E-4418-A0DC-A12E54EFCE7B}" name="Antecedência (dias)" dataDxfId="26"/>
+    <tableColumn id="4" xr3:uid="{F927B6C4-566E-48E9-9552-8EFC3D5F2C94}" name="Estadia (dias)" dataDxfId="25"/>
+    <tableColumn id="5" xr3:uid="{D989CA06-7171-4BB8-B0F0-15BE78123C53}" name="Cancelamento" dataDxfId="24"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight15" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{D7281BDC-32E5-4E20-AE3D-3FC5AFC5D146}" name="Tabela3" displayName="Tabela3" ref="A2:I14" totalsRowShown="0" headerRowDxfId="31" dataDxfId="32">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{D7281BDC-32E5-4E20-AE3D-3FC5AFC5D146}" name="Tabela3" displayName="Tabela3" ref="A2:I14" totalsRowShown="0" headerRowDxfId="23" dataDxfId="22">
   <autoFilter ref="A2:I14" xr:uid="{D7281BDC-32E5-4E20-AE3D-3FC5AFC5D146}"/>
   <tableColumns count="9">
-    <tableColumn id="1" xr3:uid="{557078F2-6B27-4EC5-A452-788CE56B68B5}" name="Mês" dataDxfId="41"/>
-    <tableColumn id="2" xr3:uid="{FC6501D9-4FF5-4172-9B7A-7AF2EBDD5FF2}" name="2019 — estimado" dataDxfId="40"/>
-    <tableColumn id="3" xr3:uid="{E304DB19-EE88-4897-944F-E8026C152604}" name="2020 — estimado" dataDxfId="39"/>
-    <tableColumn id="4" xr3:uid="{3CB96450-E09C-4C91-9C67-E7F4AE2ADF54}" name="2021 — estimado" dataDxfId="38"/>
-    <tableColumn id="5" xr3:uid="{E95F6C3E-44E9-43D7-AB7B-94D671CB81BD}" name="2022 — estimado" dataDxfId="37"/>
-    <tableColumn id="6" xr3:uid="{13E74674-2895-4083-B3DB-13DDD4DC0748}" name="2023 — estimado" dataDxfId="36"/>
-    <tableColumn id="7" xr3:uid="{D3938901-2549-44FD-ACD0-A76842E71178}" name="2024" dataDxfId="35"/>
-    <tableColumn id="8" xr3:uid="{C4D2DF9A-8DC4-452A-B503-5CC8EE8737F5}" name="2025 — estimado" dataDxfId="34"/>
-    <tableColumn id="9" xr3:uid="{08EEE0B1-E002-457F-B931-06C2599FDF1E}" name="2026" dataDxfId="33"/>
+    <tableColumn id="1" xr3:uid="{557078F2-6B27-4EC5-A452-788CE56B68B5}" name="Mês" dataDxfId="21"/>
+    <tableColumn id="2" xr3:uid="{FC6501D9-4FF5-4172-9B7A-7AF2EBDD5FF2}" name="2019 — estimado" dataDxfId="20"/>
+    <tableColumn id="3" xr3:uid="{E304DB19-EE88-4897-944F-E8026C152604}" name="2020 — estimado" dataDxfId="19"/>
+    <tableColumn id="4" xr3:uid="{3CB96450-E09C-4C91-9C67-E7F4AE2ADF54}" name="2021 — estimado" dataDxfId="18"/>
+    <tableColumn id="5" xr3:uid="{E95F6C3E-44E9-43D7-AB7B-94D671CB81BD}" name="2022 — estimado" dataDxfId="17"/>
+    <tableColumn id="6" xr3:uid="{13E74674-2895-4083-B3DB-13DDD4DC0748}" name="2023 — estimado" dataDxfId="16"/>
+    <tableColumn id="7" xr3:uid="{D3938901-2549-44FD-ACD0-A76842E71178}" name="2024" dataDxfId="15"/>
+    <tableColumn id="8" xr3:uid="{C4D2DF9A-8DC4-452A-B503-5CC8EE8737F5}" name="2025 — estimado" dataDxfId="14"/>
+    <tableColumn id="9" xr3:uid="{08EEE0B1-E002-457F-B931-06C2599FDF1E}" name="2026" dataDxfId="13"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight15" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{A27F8BC1-C9A0-4BCF-A0FD-4ED06EB404EE}" name="Tabela36" displayName="Tabela36" ref="A2:I14" totalsRowShown="0" headerRowDxfId="17" dataDxfId="16">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{A27F8BC1-C9A0-4BCF-A0FD-4ED06EB404EE}" name="Tabela36" displayName="Tabela36" ref="A2:I14" totalsRowShown="0" headerRowDxfId="41" dataDxfId="40">
   <autoFilter ref="A2:I14" xr:uid="{A27F8BC1-C9A0-4BCF-A0FD-4ED06EB404EE}"/>
   <tableColumns count="9">
-    <tableColumn id="1" xr3:uid="{F88890FF-4023-41E6-A916-1FDCCBD9DF45}" name="Mês" dataDxfId="15"/>
-    <tableColumn id="2" xr3:uid="{06ACA917-75A3-4A3B-8BFE-56A5E1871762}" name="2019 — estimado" dataDxfId="12"/>
-    <tableColumn id="3" xr3:uid="{2AEF44D3-449E-435C-AA4A-9F98B0236F5E}" name="2020 — estimado" dataDxfId="14"/>
-    <tableColumn id="4" xr3:uid="{86DE37B6-E5C0-42A3-9AE0-D148271F1119}" name="2021 — estimado" dataDxfId="13"/>
-    <tableColumn id="5" xr3:uid="{587AE4DC-216B-406F-9338-5034B163A0CF}" name="2022 — estimado" dataDxfId="11"/>
-    <tableColumn id="6" xr3:uid="{91A0E575-2FF0-4EEF-86E3-0BEE2ADABD8B}" name="2023 — estimado" dataDxfId="10"/>
-    <tableColumn id="7" xr3:uid="{A2052BD7-20A1-468D-8AC3-1FDE63F0CFDA}" name="2024" dataDxfId="9"/>
-    <tableColumn id="8" xr3:uid="{C5762637-6876-491A-B76C-85B59D775A89}" name="2025 — estimado" dataDxfId="1"/>
-    <tableColumn id="9" xr3:uid="{7D2F5D9E-3531-46ED-BBA1-E8F28D50DA2D}" name="2026" dataDxfId="0"/>
+    <tableColumn id="1" xr3:uid="{F88890FF-4023-41E6-A916-1FDCCBD9DF45}" name="Mês" dataDxfId="39"/>
+    <tableColumn id="2" xr3:uid="{06ACA917-75A3-4A3B-8BFE-56A5E1871762}" name="2019 — estimado" dataDxfId="38"/>
+    <tableColumn id="3" xr3:uid="{2AEF44D3-449E-435C-AA4A-9F98B0236F5E}" name="2020 — estimado" dataDxfId="37"/>
+    <tableColumn id="4" xr3:uid="{86DE37B6-E5C0-42A3-9AE0-D148271F1119}" name="2021 — estimado" dataDxfId="36"/>
+    <tableColumn id="5" xr3:uid="{587AE4DC-216B-406F-9338-5034B163A0CF}" name="2022 — estimado" dataDxfId="35"/>
+    <tableColumn id="6" xr3:uid="{91A0E575-2FF0-4EEF-86E3-0BEE2ADABD8B}" name="2023 — estimado" dataDxfId="34"/>
+    <tableColumn id="7" xr3:uid="{A2052BD7-20A1-468D-8AC3-1FDE63F0CFDA}" name="2024" dataDxfId="33"/>
+    <tableColumn id="8" xr3:uid="{C5762637-6876-491A-B76C-85B59D775A89}" name="2025 — estimado" dataDxfId="32"/>
+    <tableColumn id="9" xr3:uid="{7D2F5D9E-3531-46ED-BBA1-E8F28D50DA2D}" name="2026" dataDxfId="31"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight15" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{2367BDA0-32F4-40A7-9147-A0804C6AD758}" name="Tabela6" displayName="Tabela6" ref="A1:E13" totalsRowShown="0" headerRowDxfId="3" dataDxfId="2" headerRowCellStyle="Porcentagem" dataCellStyle="Porcentagem">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{2367BDA0-32F4-40A7-9147-A0804C6AD758}" name="Tabela6" displayName="Tabela6" ref="A1:E13" totalsRowShown="0" headerRowDxfId="6" dataDxfId="5" headerRowCellStyle="Porcentagem" dataCellStyle="Porcentagem">
   <autoFilter ref="A1:E13" xr:uid="{2367BDA0-32F4-40A7-9147-A0804C6AD758}"/>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{37446CC3-89B5-40E6-859D-2A0B1FA1E482}" name="Mês" dataDxfId="8" dataCellStyle="Porcentagem"/>
-    <tableColumn id="2" xr3:uid="{E97CADDC-C26E-4FEE-9236-4C802EE62EFA}" name="2023" dataDxfId="7" dataCellStyle="Porcentagem"/>
-    <tableColumn id="3" xr3:uid="{AB4C0CB3-FF8C-4487-864C-1F3DC073DB33}" name="2024" dataDxfId="6" dataCellStyle="Porcentagem"/>
-    <tableColumn id="4" xr3:uid="{73595430-6CF3-4BA8-BBA5-2EE22115F199}" name="2025" dataDxfId="5" dataCellStyle="Porcentagem"/>
-    <tableColumn id="5" xr3:uid="{A39EF228-516D-483D-B3AC-54AC2DBF9A10}" name="2026" dataDxfId="4" dataCellStyle="Porcentagem"/>
+    <tableColumn id="1" xr3:uid="{37446CC3-89B5-40E6-859D-2A0B1FA1E482}" name="Mês" dataDxfId="4" dataCellStyle="Porcentagem"/>
+    <tableColumn id="2" xr3:uid="{E97CADDC-C26E-4FEE-9236-4C802EE62EFA}" name="2023" dataDxfId="3" dataCellStyle="Porcentagem"/>
+    <tableColumn id="3" xr3:uid="{AB4C0CB3-FF8C-4487-864C-1F3DC073DB33}" name="2024" dataDxfId="2" dataCellStyle="Porcentagem"/>
+    <tableColumn id="4" xr3:uid="{73595430-6CF3-4BA8-BBA5-2EE22115F199}" name="2025" dataDxfId="1" dataCellStyle="Porcentagem"/>
+    <tableColumn id="5" xr3:uid="{A39EF228-516D-483D-B3AC-54AC2DBF9A10}" name="2026" dataDxfId="0" dataCellStyle="Porcentagem"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight15" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{4ACC621C-83CC-4E84-BACF-0AD44998C40F}" name="Tabela4" displayName="Tabela4" ref="A2:D12" totalsRowShown="0" headerRowDxfId="25" dataDxfId="26">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{4ACC621C-83CC-4E84-BACF-0AD44998C40F}" name="Tabela4" displayName="Tabela4" ref="A2:D12" totalsRowShown="0" headerRowDxfId="12" dataDxfId="11">
   <autoFilter ref="A2:D12" xr:uid="{4ACC621C-83CC-4E84-BACF-0AD44998C40F}"/>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{66018939-900B-4145-9048-4C1F5AB47A70}" name="Ano" dataDxfId="30"/>
-    <tableColumn id="2" xr3:uid="{917F8049-8535-44E5-A93A-529B634BADE0}" name="Grupo" dataDxfId="29"/>
-    <tableColumn id="3" xr3:uid="{2C71AD3B-FA79-4FFF-B581-A35F5DC30C99}" name="Categoria" dataDxfId="28"/>
-    <tableColumn id="4" xr3:uid="{B307E581-5620-46E4-989D-A6116700E841}" name="Participação" dataDxfId="27"/>
+    <tableColumn id="1" xr3:uid="{66018939-900B-4145-9048-4C1F5AB47A70}" name="Ano" dataDxfId="10"/>
+    <tableColumn id="2" xr3:uid="{917F8049-8535-44E5-A93A-529B634BADE0}" name="Grupo" dataDxfId="9"/>
+    <tableColumn id="3" xr3:uid="{2C71AD3B-FA79-4FFF-B581-A35F5DC30C99}" name="Categoria" dataDxfId="8"/>
+    <tableColumn id="4" xr3:uid="{B307E581-5620-46E4-989D-A6116700E841}" name="Participação" dataDxfId="7"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight15" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -968,13 +962,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="15" t="s">
+      <c r="A1" s="17" t="s">
         <v>41</v>
       </c>
-      <c r="B1" s="15"/>
-      <c r="C1" s="15"/>
-      <c r="D1" s="15"/>
-      <c r="E1" s="15"/>
+      <c r="B1" s="17"/>
+      <c r="C1" s="17"/>
+      <c r="D1" s="17"/>
+      <c r="E1" s="17"/>
     </row>
     <row r="2" spans="1:9" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
@@ -994,19 +988,19 @@
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A3" s="9">
+      <c r="A3" s="1">
         <v>2019</v>
       </c>
-      <c r="B3" s="10">
+      <c r="B3" s="4">
         <v>432</v>
       </c>
       <c r="C3" s="8">
         <v>54</v>
       </c>
-      <c r="D3" s="16">
+      <c r="D3" s="13">
         <v>3.3</v>
       </c>
-      <c r="E3" s="12">
+      <c r="E3" s="10">
         <v>0.3</v>
       </c>
       <c r="F3" s="6"/>
@@ -1018,16 +1012,16 @@
       <c r="A4" s="8">
         <v>2020</v>
       </c>
-      <c r="B4" s="10">
+      <c r="B4" s="4">
         <v>412</v>
       </c>
-      <c r="C4" s="13">
+      <c r="C4" s="11">
         <v>52</v>
       </c>
-      <c r="D4" s="17">
+      <c r="D4" s="14">
         <v>3.1</v>
       </c>
-      <c r="E4" s="14">
+      <c r="E4" s="12">
         <v>0.48</v>
       </c>
     </row>
@@ -1035,16 +1029,16 @@
       <c r="A5" s="8">
         <v>2021</v>
       </c>
-      <c r="B5" s="10">
+      <c r="B5" s="4">
         <v>539</v>
       </c>
       <c r="C5" s="8">
         <v>64</v>
       </c>
-      <c r="D5" s="16">
+      <c r="D5" s="13">
         <v>3.4</v>
       </c>
-      <c r="E5" s="12">
+      <c r="E5" s="10">
         <v>0.38</v>
       </c>
     </row>
@@ -1052,16 +1046,16 @@
       <c r="A6" s="8">
         <v>2022</v>
       </c>
-      <c r="B6" s="10">
+      <c r="B6" s="4">
         <v>535</v>
       </c>
-      <c r="C6" s="13">
+      <c r="C6" s="11">
         <v>53</v>
       </c>
-      <c r="D6" s="17">
+      <c r="D6" s="14">
         <v>3.2</v>
       </c>
-      <c r="E6" s="14">
+      <c r="E6" s="12">
         <v>0.27</v>
       </c>
     </row>
@@ -1069,16 +1063,16 @@
       <c r="A7" s="8">
         <v>2023</v>
       </c>
-      <c r="B7" s="10">
+      <c r="B7" s="4">
         <v>526</v>
       </c>
       <c r="C7" s="8">
         <v>53</v>
       </c>
-      <c r="D7" s="16">
+      <c r="D7" s="13">
         <v>3.2</v>
       </c>
-      <c r="E7" s="12">
+      <c r="E7" s="10">
         <v>0.26</v>
       </c>
     </row>
@@ -1086,16 +1080,16 @@
       <c r="A8" s="8">
         <v>2024</v>
       </c>
-      <c r="B8" s="10">
+      <c r="B8" s="4">
         <v>485</v>
       </c>
-      <c r="C8" s="13">
+      <c r="C8" s="11">
         <v>47</v>
       </c>
-      <c r="D8" s="17">
+      <c r="D8" s="14">
         <v>2.7</v>
       </c>
-      <c r="E8" s="14">
+      <c r="E8" s="12">
         <v>0.28999999999999998</v>
       </c>
     </row>
@@ -1103,7 +1097,7 @@
       <c r="A9" s="8">
         <v>2025</v>
       </c>
-      <c r="B9" s="10">
+      <c r="B9" s="4">
         <v>567</v>
       </c>
       <c r="C9" s="8">
@@ -1112,7 +1106,7 @@
       <c r="D9" s="8">
         <v>3.1</v>
       </c>
-      <c r="E9" s="12">
+      <c r="E9" s="10">
         <v>0.22</v>
       </c>
     </row>
@@ -1120,16 +1114,16 @@
       <c r="A10" s="8">
         <v>2026</v>
       </c>
-      <c r="B10" s="10">
+      <c r="B10" s="4">
         <v>535</v>
       </c>
       <c r="C10" s="8">
-        <v>86</v>
+        <v>75.2</v>
       </c>
       <c r="D10" s="8">
-        <v>3.17</v>
-      </c>
-      <c r="E10" s="12">
+        <v>3.05</v>
+      </c>
+      <c r="E10" s="10">
         <v>0.21</v>
       </c>
     </row>
@@ -1161,17 +1155,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="15" t="s">
+      <c r="A1" s="17" t="s">
         <v>40</v>
       </c>
-      <c r="B1" s="15"/>
-      <c r="C1" s="15"/>
-      <c r="D1" s="15"/>
-      <c r="E1" s="15"/>
-      <c r="F1" s="15"/>
-      <c r="G1" s="15"/>
-      <c r="H1" s="15"/>
-      <c r="I1" s="15"/>
+      <c r="B1" s="17"/>
+      <c r="C1" s="17"/>
+      <c r="D1" s="17"/>
+      <c r="E1" s="17"/>
+      <c r="F1" s="17"/>
+      <c r="G1" s="17"/>
+      <c r="H1" s="17"/>
+      <c r="I1" s="17"/>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
@@ -1315,7 +1309,7 @@
         <v>524</v>
       </c>
       <c r="I6" s="7">
-        <v>530.61</v>
+        <v>529.66</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
@@ -1344,7 +1338,7 @@
         <v>566</v>
       </c>
       <c r="I7" s="7">
-        <v>562.15</v>
+        <v>564.34</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
@@ -1373,7 +1367,7 @@
         <v>610</v>
       </c>
       <c r="I8" s="7">
-        <v>598.39</v>
+        <v>599.95000000000005</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
@@ -1401,6 +1395,9 @@
       <c r="H9" s="4">
         <v>608</v>
       </c>
+      <c r="I9" s="7">
+        <v>613.21</v>
+      </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
@@ -1427,6 +1424,9 @@
       <c r="H10" s="4">
         <v>597</v>
       </c>
+      <c r="I10" s="7">
+        <v>575.72</v>
+      </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
@@ -1453,6 +1453,9 @@
       <c r="H11" s="4">
         <v>626</v>
       </c>
+      <c r="I11" s="7">
+        <v>632.07000000000005</v>
+      </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
@@ -1479,6 +1482,7 @@
       <c r="H12" s="4">
         <v>686</v>
       </c>
+      <c r="I12" s="7"/>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
@@ -1570,17 +1574,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A1" s="18" t="s">
+      <c r="A1" s="16" t="s">
         <v>42</v>
       </c>
-      <c r="B1" s="18"/>
-      <c r="C1" s="18"/>
-      <c r="D1" s="18"/>
-      <c r="E1" s="18"/>
-      <c r="F1" s="18"/>
-      <c r="G1" s="18"/>
-      <c r="H1" s="18"/>
-      <c r="I1" s="18"/>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
+      <c r="F1" s="16"/>
+      <c r="G1" s="16"/>
+      <c r="H1" s="16"/>
+      <c r="I1" s="16"/>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
@@ -1638,16 +1642,16 @@
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="11"/>
+      <c r="B4" s="9"/>
       <c r="C4" s="4"/>
       <c r="D4" s="4"/>
-      <c r="E4" s="11">
+      <c r="E4" s="9">
         <v>45</v>
       </c>
-      <c r="F4" s="11">
+      <c r="F4" s="9">
         <v>65</v>
       </c>
-      <c r="G4" s="11">
+      <c r="G4" s="9">
         <v>62</v>
       </c>
       <c r="H4" s="3">
@@ -1684,16 +1688,16 @@
       <c r="A6" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="11"/>
+      <c r="B6" s="9"/>
       <c r="C6" s="4"/>
       <c r="D6" s="4"/>
-      <c r="E6" s="11">
+      <c r="E6" s="9">
         <v>64</v>
       </c>
-      <c r="F6" s="11">
+      <c r="F6" s="9">
         <v>110</v>
       </c>
-      <c r="G6" s="11">
+      <c r="G6" s="9">
         <v>66</v>
       </c>
       <c r="H6" s="3">
@@ -1730,16 +1734,16 @@
       <c r="A8" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B8" s="11"/>
+      <c r="B8" s="9"/>
       <c r="C8" s="4"/>
       <c r="D8" s="4"/>
-      <c r="E8" s="11">
+      <c r="E8" s="9">
         <v>83</v>
       </c>
-      <c r="F8" s="11">
+      <c r="F8" s="9">
         <v>92</v>
       </c>
-      <c r="G8" s="11">
+      <c r="G8" s="9">
         <v>95</v>
       </c>
       <c r="H8" s="3">
@@ -1768,28 +1772,32 @@
       <c r="H9" s="3">
         <v>99</v>
       </c>
-      <c r="I9" s="3"/>
+      <c r="I9" s="3">
+        <v>110</v>
+      </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B10" s="11"/>
+      <c r="B10" s="9"/>
       <c r="C10" s="4"/>
       <c r="D10" s="4"/>
-      <c r="E10" s="11">
+      <c r="E10" s="9">
         <v>76</v>
       </c>
-      <c r="F10" s="11">
+      <c r="F10" s="9">
         <v>76</v>
       </c>
-      <c r="G10" s="11">
+      <c r="G10" s="9">
         <v>80</v>
       </c>
       <c r="H10" s="3">
         <v>90</v>
       </c>
-      <c r="I10" s="3"/>
+      <c r="I10" s="3">
+        <v>80</v>
+      </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
@@ -1810,22 +1818,24 @@
       <c r="H11" s="3">
         <v>81</v>
       </c>
-      <c r="I11" s="3"/>
+      <c r="I11" s="3">
+        <v>78</v>
+      </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B12" s="11"/>
+      <c r="B12" s="9"/>
       <c r="C12" s="4"/>
       <c r="D12" s="4"/>
-      <c r="E12" s="11">
+      <c r="E12" s="9">
         <v>58</v>
       </c>
-      <c r="F12" s="11">
+      <c r="F12" s="9">
         <v>60</v>
       </c>
-      <c r="G12" s="11">
+      <c r="G12" s="9">
         <v>81</v>
       </c>
       <c r="H12" s="3">
@@ -1858,16 +1868,16 @@
       <c r="A14" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B14" s="11"/>
+      <c r="B14" s="9"/>
       <c r="C14" s="4"/>
       <c r="D14" s="4"/>
-      <c r="E14" s="11">
+      <c r="E14" s="9">
         <v>61</v>
       </c>
-      <c r="F14" s="11">
+      <c r="F14" s="9">
         <v>46</v>
       </c>
-      <c r="G14" s="11">
+      <c r="G14" s="9">
         <v>74</v>
       </c>
       <c r="H14" s="3">
@@ -1899,235 +1909,239 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{967D84A5-916C-4D48-B4A4-E144D85226C6}">
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.140625" style="8" bestFit="1" customWidth="1"/>
     <col min="2" max="16384" width="9.140625" style="8"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="19" t="s">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="19" t="s">
+      <c r="B1" s="15" t="s">
         <v>21</v>
       </c>
-      <c r="C1" s="19" t="s">
+      <c r="C1" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="D1" s="19" t="s">
+      <c r="D1" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="E1" s="19" t="s">
+      <c r="E1" s="15" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="19" t="s">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" s="15" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="19">
+      <c r="B2" s="15">
         <v>0.6405806451612901</v>
       </c>
-      <c r="C2" s="19">
+      <c r="C2" s="15">
         <v>0.59816129032258059</v>
       </c>
-      <c r="D2" s="19">
+      <c r="D2" s="15">
         <v>0.61593548387096775</v>
       </c>
-      <c r="E2" s="19">
+      <c r="E2" s="15">
         <v>0.66245161290322574</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" s="19" t="s">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" s="15" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="19">
+      <c r="B3" s="15">
         <v>0.45310714285714282</v>
       </c>
-      <c r="C3" s="19">
+      <c r="C3" s="15">
         <v>0.42665517241379308</v>
       </c>
-      <c r="D3" s="19">
+      <c r="D3" s="15">
         <v>0.36792857142857144</v>
       </c>
-      <c r="E3" s="19">
+      <c r="E3" s="15">
         <v>0.45996428571428566</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" s="19" t="s">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="15" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="19">
+      <c r="B4" s="15">
         <v>0.46390322580645155</v>
       </c>
-      <c r="C4" s="19">
+      <c r="C4" s="15">
         <v>0.52570967741935493</v>
       </c>
-      <c r="D4" s="19">
+      <c r="D4" s="15">
         <v>0.48319354838709677</v>
       </c>
-      <c r="E4" s="19">
+      <c r="E4" s="15">
         <v>0.52851612903225809</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" s="19" t="s">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="19">
+      <c r="B5" s="15">
         <v>0.56256666666666655</v>
       </c>
-      <c r="C5" s="19">
+      <c r="C5" s="15">
         <v>0.46443333333333336</v>
       </c>
-      <c r="D5" s="19">
+      <c r="D5" s="15">
         <v>0.5605</v>
       </c>
-      <c r="E5" s="19">
+      <c r="E5" s="15">
         <v>0.54646666666666666</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" s="19" t="s">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="B6" s="19">
+      <c r="B6" s="15">
         <v>0.60283870967741937</v>
       </c>
-      <c r="C6" s="19">
+      <c r="C6" s="15">
         <v>0.13274193548387095</v>
       </c>
-      <c r="D6" s="19">
+      <c r="D6" s="15">
         <v>0.59309677419354823</v>
       </c>
-      <c r="E6" s="19">
+      <c r="E6" s="15">
         <v>0.61687096774193551</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" s="19" t="s">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="15" t="s">
         <v>7</v>
       </c>
-      <c r="B7" s="19">
+      <c r="B7" s="15">
         <v>0.63456666666666672</v>
       </c>
-      <c r="C7" s="19">
+      <c r="C7" s="15">
         <v>0.2790333333333333</v>
       </c>
-      <c r="D7" s="19">
+      <c r="D7" s="15">
         <v>0.63296666666666646</v>
       </c>
-      <c r="E7" s="19">
+      <c r="E7" s="15">
         <v>0.62943333333333329</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8" s="19" t="s">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="15" t="s">
         <v>8</v>
       </c>
-      <c r="B8" s="19">
+      <c r="B8" s="15">
         <v>0.77338709677419337</v>
       </c>
-      <c r="C8" s="19">
+      <c r="C8" s="15">
         <v>0.50370967741935491</v>
       </c>
-      <c r="D8" s="19">
+      <c r="D8" s="15">
         <v>0.78164516129032269</v>
       </c>
-      <c r="E8" s="19">
-        <v>0.7332142857142856</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A9" s="19" t="s">
+      <c r="E8" s="15">
+        <v>0.73321428571428604</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="B9" s="19">
+      <c r="B9" s="15">
         <v>0.64529032258064511</v>
       </c>
-      <c r="C9" s="19">
+      <c r="C9" s="15">
         <v>0.44554838709677419</v>
       </c>
-      <c r="D9" s="19">
+      <c r="D9" s="15">
         <v>0.64403225806451614</v>
       </c>
-      <c r="E9" s="19" t="s">
+      <c r="E9" s="15">
+        <v>0.61299999999999999</v>
+      </c>
+      <c r="F9" s="15" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A10" s="19" t="s">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="B10" s="19">
+      <c r="B10" s="15">
         <v>0.60093333333333321</v>
       </c>
-      <c r="C10" s="19">
+      <c r="C10" s="15">
         <v>0.39256666666666679</v>
       </c>
-      <c r="D10" s="19">
+      <c r="D10" s="15">
         <v>0.60516666666666674</v>
       </c>
-      <c r="E10" s="19" t="s">
+      <c r="E10" s="15">
+        <v>0.58899999999999997</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="B11" s="15">
+        <v>0.57161290322580638</v>
+      </c>
+      <c r="C11" s="15">
+        <v>0.39503225806451614</v>
+      </c>
+      <c r="D11" s="15">
+        <v>0.6365483870967743</v>
+      </c>
+      <c r="E11" s="15" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A11" s="19" t="s">
-        <v>11</v>
-      </c>
-      <c r="B11" s="19">
-        <v>0.57161290322580638</v>
-      </c>
-      <c r="C11" s="19">
-        <v>0.39503225806451614</v>
-      </c>
-      <c r="D11" s="19">
-        <v>0.6365483870967743</v>
-      </c>
-      <c r="E11" s="19" t="s">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="B12" s="15">
+        <v>0.68399999999999994</v>
+      </c>
+      <c r="C12" s="15">
+        <v>0.59243333333333337</v>
+      </c>
+      <c r="D12" s="15">
+        <v>0.73589999999999978</v>
+      </c>
+      <c r="E12" s="15" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A12" s="19" t="s">
-        <v>12</v>
-      </c>
-      <c r="B12" s="19">
-        <v>0.68399999999999994</v>
-      </c>
-      <c r="C12" s="19">
-        <v>0.59243333333333337</v>
-      </c>
-      <c r="D12" s="19">
-        <v>0.73589999999999978</v>
-      </c>
-      <c r="E12" s="19" t="s">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="B13" s="15">
+        <v>0.6832258064516129</v>
+      </c>
+      <c r="C13" s="15">
+        <v>0.66848387096774198</v>
+      </c>
+      <c r="D13" s="15">
+        <v>0.76399999999999979</v>
+      </c>
+      <c r="E13" s="15" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A13" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="B13" s="19">
-        <v>0.6832258064516129</v>
-      </c>
-      <c r="C13" s="19">
-        <v>0.66848387096774198</v>
-      </c>
-      <c r="D13" s="19">
-        <v>0.76399999999999979</v>
-      </c>
-      <c r="E13" s="19" t="s">
-        <v>43</v>
-      </c>
-    </row>
   </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <tableParts count="1">
     <tablePart r:id="rId1"/>
@@ -2148,12 +2162,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="15" t="s">
+      <c r="A1" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="B1" s="15"/>
-      <c r="C1" s="15"/>
-      <c r="D1" s="15"/>
+      <c r="B1" s="17"/>
+      <c r="C1" s="17"/>
+      <c r="D1" s="17"/>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
@@ -2179,21 +2193,21 @@
       <c r="C3" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="D3" s="12">
+      <c r="D3" s="10">
         <v>0.96</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" s="13">
+      <c r="A4" s="11">
         <v>2022</v>
       </c>
-      <c r="B4" s="13" t="s">
+      <c r="B4" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="C4" s="13" t="s">
+      <c r="C4" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="D4" s="14">
+      <c r="D4" s="12">
         <v>0.04</v>
       </c>
     </row>
@@ -2207,21 +2221,21 @@
       <c r="C5" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="D5" s="12">
+      <c r="D5" s="10">
         <v>0.94</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" s="13">
+      <c r="A6" s="11">
         <v>2023</v>
       </c>
-      <c r="B6" s="13" t="s">
+      <c r="B6" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="C6" s="13" t="s">
+      <c r="C6" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="D6" s="14">
+      <c r="D6" s="12">
         <v>0.06</v>
       </c>
     </row>
@@ -2235,21 +2249,21 @@
       <c r="C7" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="D7" s="12">
+      <c r="D7" s="10">
         <v>0.93</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A8" s="13">
+      <c r="A8" s="11">
         <v>2024</v>
       </c>
-      <c r="B8" s="13" t="s">
+      <c r="B8" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="C8" s="13" t="s">
+      <c r="C8" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="D8" s="14">
+      <c r="D8" s="12">
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
@@ -2263,21 +2277,21 @@
       <c r="C9" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="D9" s="12">
+      <c r="D9" s="10">
         <v>0.73</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10" s="13">
+      <c r="A10" s="11">
         <v>2024</v>
       </c>
-      <c r="B10" s="13" t="s">
+      <c r="B10" s="11" t="s">
         <v>31</v>
       </c>
-      <c r="C10" s="13" t="s">
+      <c r="C10" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="D10" s="14">
+      <c r="D10" s="12">
         <v>0.18</v>
       </c>
     </row>
@@ -2291,21 +2305,21 @@
       <c r="C11" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="D11" s="12">
+      <c r="D11" s="10">
         <v>0.08</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A12" s="13">
+      <c r="A12" s="11">
         <v>2024</v>
       </c>
-      <c r="B12" s="13" t="s">
+      <c r="B12" s="11" t="s">
         <v>31</v>
       </c>
-      <c r="C12" s="13" t="s">
+      <c r="C12" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="D12" s="14">
+      <c r="D12" s="12">
         <v>0.01</v>
       </c>
     </row>
